--- a/docs/timesheet.xlsx
+++ b/docs/timesheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huawei\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huawei\OneDrive\Desktop\RPG game project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DD73E5-FD47-46FC-A966-9D53D1D5CBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{911AA0C8-C7E8-43FE-85C0-FEDC9C2BB6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Timesheet" sheetId="1" r:id="rId1"/>
@@ -46,13 +46,13 @@
     <t>0:30</t>
   </si>
   <si>
-    <t>2:30</t>
-  </si>
-  <si>
     <t>repository setup</t>
   </si>
   <si>
     <t>Editing the note's ideas</t>
+  </si>
+  <si>
+    <t>2:20</t>
   </si>
 </sst>
 </file>
@@ -405,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
@@ -436,7 +436,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2">
         <v>0.77083333333333337</v>
@@ -453,16 +453,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2">
         <v>0.8125</v>
       </c>
       <c r="D3" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.90972222222222221</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docs/timesheet.xlsx
+++ b/docs/timesheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huawei\OneDrive\Desktop\RPG game project\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huawei\OneDrive\Desktop\Renad\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{911AA0C8-C7E8-43FE-85C0-FEDC9C2BB6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E23BD9C-3CFC-478A-8AA5-88A12B49B0E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3048" yWindow="936" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Timesheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Date</t>
   </si>
@@ -38,9 +38,6 @@
   </si>
   <si>
     <t>22/06/2026</t>
-  </si>
-  <si>
-    <t>23/06/2026</t>
   </si>
   <si>
     <t>0:30</t>
@@ -436,7 +433,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2">
         <v>0.77083333333333337</v>
@@ -445,15 +442,15 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2">
         <v>0.8125</v>
@@ -462,7 +459,7 @@
         <v>0.90972222222222221</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/docs/timesheet.xlsx
+++ b/docs/timesheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huawei\OneDrive\Desktop\Renad\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E23BD9C-3CFC-478A-8AA5-88A12B49B0E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788C71EB-8DF3-4024-ABC0-7C65131FC072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3648" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Timesheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>Date</t>
   </si>
@@ -50,6 +50,15 @@
   </si>
   <si>
     <t>2:20</t>
+  </si>
+  <si>
+    <t>22.06.2026</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2:00</t>
   </si>
 </sst>
 </file>
@@ -402,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
@@ -462,6 +471,23 @@
         <v>9</v>
       </c>
     </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
